--- a/DATAFiles/Ch01/DATAfiles/compactsuv.xlsx
+++ b/DATAFiles/Ch01/DATAfiles/compactsuv.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\h69j985\Documents\GitHub\BMGT-204IS\DATAFiles\Ch01\DATAfiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5D9B8DCE-0C2B-426E-90A4-88B0F17993A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7878046-0A84-4E0F-8CA5-EAF352DF9A1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,6 @@
     <sheet name="Summary" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -804,22 +803,22 @@
     <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1536,31 +1535,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="18" x14ac:dyDescent="0.35">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="33" t="s">
         <v>41</v>
       </c>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32"/>
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
     </row>
     <row r="4" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="34" t="s">
+      <c r="A4" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="B4" s="32"/>
-      <c r="C4" s="32"/>
-      <c r="D4" s="32"/>
-      <c r="E4" s="32"/>
+      <c r="B4" s="29"/>
+      <c r="C4" s="29"/>
+      <c r="D4" s="29"/>
+      <c r="E4" s="29"/>
     </row>
     <row r="5" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
@@ -1614,13 +1613,13 @@
       </c>
     </row>
     <row r="10" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="34" t="s">
+      <c r="A10" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="B10" s="32"/>
-      <c r="C10" s="32"/>
-      <c r="D10" s="32"/>
-      <c r="E10" s="32"/>
+      <c r="B10" s="29"/>
+      <c r="C10" s="29"/>
+      <c r="D10" s="29"/>
+      <c r="E10" s="29"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="8" t="s">
@@ -1639,7 +1638,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
         <v>0</v>
       </c>
@@ -1715,7 +1714,7 @@
         <v>++ 3   ·   + 4   ·   0 7   ·   - 1</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A16" s="9" t="s">
         <v>63</v>
       </c>
@@ -1734,7 +1733,7 @@
         <v>21 to 31 mpg   ·   mean 24.4</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A17" s="9" t="s">
         <v>65</v>
       </c>
@@ -1754,13 +1753,13 @@
       </c>
     </row>
     <row r="19" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="34" t="s">
+      <c r="A19" s="28" t="s">
         <v>66</v>
       </c>
-      <c r="B19" s="32"/>
-      <c r="C19" s="32"/>
-      <c r="D19" s="32"/>
-      <c r="E19" s="32"/>
+      <c r="B19" s="29"/>
+      <c r="C19" s="29"/>
+      <c r="D19" s="29"/>
+      <c r="E19" s="29"/>
     </row>
     <row r="20" spans="1:5" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A20" s="11"/>
@@ -1877,13 +1876,13 @@
       </c>
     </row>
     <row r="28" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="34" t="s">
+      <c r="A28" s="28" t="s">
         <v>74</v>
       </c>
-      <c r="B28" s="32"/>
-      <c r="C28" s="32"/>
-      <c r="D28" s="32"/>
-      <c r="E28" s="32"/>
+      <c r="B28" s="29"/>
+      <c r="C28" s="29"/>
+      <c r="D28" s="29"/>
+      <c r="E28" s="29"/>
     </row>
     <row r="29" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A29" s="12" t="s">
@@ -1922,13 +1921,13 @@
       </c>
     </row>
     <row r="33" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="34" t="s">
+      <c r="A33" s="28" t="s">
         <v>81</v>
       </c>
-      <c r="B33" s="32"/>
-      <c r="C33" s="32"/>
-      <c r="D33" s="32"/>
-      <c r="E33" s="32"/>
+      <c r="B33" s="29"/>
+      <c r="C33" s="29"/>
+      <c r="D33" s="29"/>
+      <c r="E33" s="29"/>
     </row>
     <row r="34" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A34" s="7" t="s">
@@ -1954,19 +1953,19 @@
       <c r="A36" s="33" t="s">
         <v>84</v>
       </c>
-      <c r="B36" s="32"/>
-      <c r="C36" s="32"/>
-      <c r="D36" s="32"/>
-      <c r="E36" s="32"/>
+      <c r="B36" s="29"/>
+      <c r="C36" s="29"/>
+      <c r="D36" s="29"/>
+      <c r="E36" s="29"/>
     </row>
     <row r="38" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="34" t="s">
+      <c r="A38" s="28" t="s">
         <v>85</v>
       </c>
-      <c r="B38" s="32"/>
-      <c r="C38" s="32"/>
-      <c r="D38" s="32"/>
-      <c r="E38" s="32"/>
+      <c r="B38" s="29"/>
+      <c r="C38" s="29"/>
+      <c r="D38" s="29"/>
+      <c r="E38" s="29"/>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" s="8" t="s">
@@ -2032,19 +2031,19 @@
       <c r="A44" s="33" t="s">
         <v>98</v>
       </c>
-      <c r="B44" s="32"/>
-      <c r="C44" s="32"/>
-      <c r="D44" s="32"/>
-      <c r="E44" s="32"/>
+      <c r="B44" s="29"/>
+      <c r="C44" s="29"/>
+      <c r="D44" s="29"/>
+      <c r="E44" s="29"/>
     </row>
     <row r="46" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="34" t="s">
+      <c r="A46" s="28" t="s">
         <v>99</v>
       </c>
-      <c r="B46" s="32"/>
-      <c r="C46" s="32"/>
-      <c r="D46" s="32"/>
-      <c r="E46" s="32"/>
+      <c r="B46" s="29"/>
+      <c r="C46" s="29"/>
+      <c r="D46" s="29"/>
+      <c r="E46" s="29"/>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" s="8" t="s">
@@ -2059,7 +2058,7 @@
       <c r="D47" s="36" t="s">
         <v>103</v>
       </c>
-      <c r="E47" s="29"/>
+      <c r="E47" s="31"/>
     </row>
     <row r="48" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="14" t="s">
@@ -2071,8 +2070,8 @@
       <c r="C48" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="D48" s="28"/>
-      <c r="E48" s="29"/>
+      <c r="D48" s="34"/>
+      <c r="E48" s="31"/>
     </row>
     <row r="49" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="14" t="s">
@@ -2084,10 +2083,10 @@
       <c r="C49" s="16" t="s">
         <v>108</v>
       </c>
-      <c r="D49" s="30" t="s">
+      <c r="D49" s="32" t="s">
         <v>109</v>
       </c>
-      <c r="E49" s="29"/>
+      <c r="E49" s="31"/>
     </row>
     <row r="50" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="14" t="s">
@@ -2099,10 +2098,10 @@
       <c r="C50" s="16" t="s">
         <v>110</v>
       </c>
-      <c r="D50" s="30" t="s">
+      <c r="D50" s="32" t="s">
         <v>111</v>
       </c>
-      <c r="E50" s="29"/>
+      <c r="E50" s="31"/>
     </row>
     <row r="51" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="14" t="s">
@@ -2114,10 +2113,10 @@
       <c r="C51" s="16" t="s">
         <v>113</v>
       </c>
-      <c r="D51" s="30" t="s">
+      <c r="D51" s="32" t="s">
         <v>114</v>
       </c>
-      <c r="E51" s="29"/>
+      <c r="E51" s="31"/>
     </row>
     <row r="52" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="14" t="s">
@@ -2129,10 +2128,10 @@
       <c r="C52" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="D52" s="30" t="s">
+      <c r="D52" s="32" t="s">
         <v>117</v>
       </c>
-      <c r="E52" s="29"/>
+      <c r="E52" s="31"/>
     </row>
     <row r="53" spans="1:5" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="14" t="s">
@@ -2144,10 +2143,10 @@
       <c r="C53" s="16" t="s">
         <v>119</v>
       </c>
-      <c r="D53" s="30" t="s">
+      <c r="D53" s="32" t="s">
         <v>120</v>
       </c>
-      <c r="E53" s="29"/>
+      <c r="E53" s="31"/>
     </row>
     <row r="54" spans="1:5" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="14" t="s">
@@ -2159,10 +2158,10 @@
       <c r="C54" s="16" t="s">
         <v>122</v>
       </c>
-      <c r="D54" s="30" t="s">
+      <c r="D54" s="32" t="s">
         <v>123</v>
       </c>
-      <c r="E54" s="29"/>
+      <c r="E54" s="31"/>
     </row>
     <row r="55" spans="1:5" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="14" t="s">
@@ -2174,10 +2173,10 @@
       <c r="C55" s="16" t="s">
         <v>125</v>
       </c>
-      <c r="D55" s="30" t="s">
+      <c r="D55" s="32" t="s">
         <v>126</v>
       </c>
-      <c r="E55" s="29"/>
+      <c r="E55" s="31"/>
     </row>
     <row r="56" spans="1:5" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="14" t="s">
@@ -2189,10 +2188,10 @@
       <c r="C56" s="16" t="s">
         <v>128</v>
       </c>
-      <c r="D56" s="30" t="s">
+      <c r="D56" s="32" t="s">
         <v>129</v>
       </c>
-      <c r="E56" s="29"/>
+      <c r="E56" s="31"/>
     </row>
     <row r="57" spans="1:5" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="14" t="s">
@@ -2204,10 +2203,10 @@
       <c r="C57" s="16" t="s">
         <v>131</v>
       </c>
-      <c r="D57" s="30" t="s">
+      <c r="D57" s="32" t="s">
         <v>132</v>
       </c>
-      <c r="E57" s="29"/>
+      <c r="E57" s="31"/>
     </row>
     <row r="58" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="14" t="s">
@@ -2219,8 +2218,8 @@
       <c r="C58" s="16" t="s">
         <v>134</v>
       </c>
-      <c r="D58" s="28"/>
-      <c r="E58" s="29"/>
+      <c r="D58" s="34"/>
+      <c r="E58" s="31"/>
     </row>
     <row r="59" spans="1:5" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="14" t="s">
@@ -2232,10 +2231,10 @@
       <c r="C59" s="16" t="s">
         <v>136</v>
       </c>
-      <c r="D59" s="30" t="s">
+      <c r="D59" s="32" t="s">
         <v>137</v>
       </c>
-      <c r="E59" s="29"/>
+      <c r="E59" s="31"/>
     </row>
     <row r="60" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="14" t="s">
@@ -2247,8 +2246,8 @@
       <c r="C60" s="16" t="s">
         <v>139</v>
       </c>
-      <c r="D60" s="28"/>
-      <c r="E60" s="29"/>
+      <c r="D60" s="34"/>
+      <c r="E60" s="31"/>
     </row>
     <row r="61" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="14" t="s">
@@ -2260,10 +2259,10 @@
       <c r="C61" s="16" t="s">
         <v>141</v>
       </c>
-      <c r="D61" s="30" t="s">
+      <c r="D61" s="32" t="s">
         <v>142</v>
       </c>
-      <c r="E61" s="29"/>
+      <c r="E61" s="31"/>
     </row>
     <row r="62" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="14" t="s">
@@ -2275,10 +2274,10 @@
       <c r="C62" s="16" t="s">
         <v>144</v>
       </c>
-      <c r="D62" s="30" t="s">
+      <c r="D62" s="32" t="s">
         <v>145</v>
       </c>
-      <c r="E62" s="29"/>
+      <c r="E62" s="31"/>
     </row>
     <row r="63" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="14" t="s">
@@ -2290,10 +2289,10 @@
       <c r="C63" s="16" t="s">
         <v>148</v>
       </c>
-      <c r="D63" s="30" t="s">
+      <c r="D63" s="32" t="s">
         <v>149</v>
       </c>
-      <c r="E63" s="29"/>
+      <c r="E63" s="31"/>
     </row>
     <row r="64" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="14" t="s">
@@ -2305,10 +2304,10 @@
       <c r="C64" s="16" t="s">
         <v>152</v>
       </c>
-      <c r="D64" s="30" t="s">
+      <c r="D64" s="32" t="s">
         <v>153</v>
       </c>
-      <c r="E64" s="29"/>
+      <c r="E64" s="31"/>
     </row>
     <row r="65" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="14" t="s">
@@ -2320,10 +2319,10 @@
       <c r="C65" s="16" t="s">
         <v>155</v>
       </c>
-      <c r="D65" s="30" t="s">
+      <c r="D65" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="E65" s="29"/>
+      <c r="E65" s="31"/>
     </row>
     <row r="66" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="14" t="s">
@@ -2335,8 +2334,8 @@
       <c r="C66" s="16" t="s">
         <v>158</v>
       </c>
-      <c r="D66" s="28"/>
-      <c r="E66" s="29"/>
+      <c r="D66" s="34"/>
+      <c r="E66" s="31"/>
     </row>
     <row r="67" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="14" t="s">
@@ -2348,8 +2347,8 @@
       <c r="C67" s="16" t="s">
         <v>160</v>
       </c>
-      <c r="D67" s="28"/>
-      <c r="E67" s="29"/>
+      <c r="D67" s="34"/>
+      <c r="E67" s="31"/>
     </row>
     <row r="68" spans="1:5" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="14" t="s">
@@ -2361,10 +2360,10 @@
       <c r="C68" s="16" t="s">
         <v>162</v>
       </c>
-      <c r="D68" s="30" t="s">
+      <c r="D68" s="32" t="s">
         <v>163</v>
       </c>
-      <c r="E68" s="29"/>
+      <c r="E68" s="31"/>
     </row>
     <row r="69" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="14" t="s">
@@ -2376,8 +2375,8 @@
       <c r="C69" s="16" t="s">
         <v>166</v>
       </c>
-      <c r="D69" s="28"/>
-      <c r="E69" s="29"/>
+      <c r="D69" s="34"/>
+      <c r="E69" s="31"/>
     </row>
     <row r="70" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="17" t="s">
@@ -2389,8 +2388,8 @@
       <c r="C70" s="19" t="s">
         <v>169</v>
       </c>
-      <c r="D70" s="35"/>
-      <c r="E70" s="29"/>
+      <c r="D70" s="30"/>
+      <c r="E70" s="31"/>
     </row>
     <row r="71" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="17" t="s">
@@ -2402,8 +2401,8 @@
       <c r="C71" s="19" t="s">
         <v>171</v>
       </c>
-      <c r="D71" s="35"/>
-      <c r="E71" s="29"/>
+      <c r="D71" s="30"/>
+      <c r="E71" s="31"/>
     </row>
     <row r="72" spans="1:5" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="17" t="s">
@@ -2415,8 +2414,8 @@
       <c r="C72" s="19" t="s">
         <v>173</v>
       </c>
-      <c r="D72" s="35"/>
-      <c r="E72" s="29"/>
+      <c r="D72" s="30"/>
+      <c r="E72" s="31"/>
     </row>
     <row r="73" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="17" t="s">
@@ -2428,8 +2427,8 @@
       <c r="C73" s="19" t="s">
         <v>175</v>
       </c>
-      <c r="D73" s="35"/>
-      <c r="E73" s="29"/>
+      <c r="D73" s="30"/>
+      <c r="E73" s="31"/>
     </row>
     <row r="74" spans="1:5" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="17" t="s">
@@ -2441,8 +2440,8 @@
       <c r="C74" s="19" t="s">
         <v>178</v>
       </c>
-      <c r="D74" s="35"/>
-      <c r="E74" s="29"/>
+      <c r="D74" s="30"/>
+      <c r="E74" s="31"/>
     </row>
     <row r="75" spans="1:5" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="17" t="s">
@@ -2454,25 +2453,39 @@
       <c r="C75" s="19" t="s">
         <v>180</v>
       </c>
-      <c r="D75" s="35"/>
-      <c r="E75" s="29"/>
+      <c r="D75" s="30"/>
+      <c r="E75" s="31"/>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76" s="33" t="s">
         <v>181</v>
       </c>
-      <c r="B76" s="32"/>
-      <c r="C76" s="32"/>
-      <c r="D76" s="32"/>
-      <c r="E76" s="32"/>
+      <c r="B76" s="29"/>
+      <c r="C76" s="29"/>
+      <c r="D76" s="29"/>
+      <c r="E76" s="29"/>
     </row>
   </sheetData>
   <mergeCells count="41">
-    <mergeCell ref="A19:E19"/>
-    <mergeCell ref="D73:E73"/>
-    <mergeCell ref="D54:E54"/>
-    <mergeCell ref="D50:E50"/>
-    <mergeCell ref="D59:E59"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="D65:E65"/>
+    <mergeCell ref="D52:E52"/>
+    <mergeCell ref="D49:E49"/>
+    <mergeCell ref="D57:E57"/>
+    <mergeCell ref="D61:E61"/>
+    <mergeCell ref="A46:E46"/>
+    <mergeCell ref="D47:E47"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="D75:E75"/>
+    <mergeCell ref="D53:E53"/>
+    <mergeCell ref="D72:E72"/>
+    <mergeCell ref="D69:E69"/>
+    <mergeCell ref="D60:E60"/>
+    <mergeCell ref="D63:E63"/>
     <mergeCell ref="A76:E76"/>
     <mergeCell ref="A33:E33"/>
     <mergeCell ref="D62:E62"/>
@@ -2489,26 +2502,12 @@
     <mergeCell ref="D51:E51"/>
     <mergeCell ref="D70:E70"/>
     <mergeCell ref="D66:E66"/>
+    <mergeCell ref="A19:E19"/>
+    <mergeCell ref="D73:E73"/>
+    <mergeCell ref="D54:E54"/>
+    <mergeCell ref="D50:E50"/>
+    <mergeCell ref="D59:E59"/>
     <mergeCell ref="D48:E48"/>
-    <mergeCell ref="D75:E75"/>
-    <mergeCell ref="D53:E53"/>
-    <mergeCell ref="D72:E72"/>
-    <mergeCell ref="D69:E69"/>
-    <mergeCell ref="D60:E60"/>
-    <mergeCell ref="D63:E63"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A36:E36"/>
-    <mergeCell ref="D65:E65"/>
-    <mergeCell ref="D52:E52"/>
-    <mergeCell ref="D49:E49"/>
-    <mergeCell ref="D57:E57"/>
-    <mergeCell ref="D61:E61"/>
-    <mergeCell ref="A46:E46"/>
-    <mergeCell ref="D47:E47"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="A28:E28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
